--- a/excel_reports/backtest_compare/s12/compare_s12_M5_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s12/compare_s12_M5_20260528_0800_20260608_1000.xlsx
@@ -16,10 +16,10 @@
     <sheet name="Gap Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Compare'!$A$1:$BK$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Mismatches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$8</definedName>
   </definedNames>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09 20:57:04</t>
+          <t>2026-06-18 17:19:59</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK21"/>
+  <dimension ref="A1:BK17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1467,13 +1467,13 @@
       <c r="AB5" s="8" t="inlineStr"/>
       <c r="AC5" s="8" t="inlineStr"/>
       <c r="AD5" s="9" t="n">
-        <v>46171.69791666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>46171.70138888889</v>
+        <v>46171.92013888889</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>4539.24</v>
+        <v>4580.38</v>
       </c>
       <c r="AG5" s="8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="AH5" s="8" t="n">
-        <v>4537.24</v>
+        <v>4578.38</v>
       </c>
       <c r="AI5" s="8" t="n">
         <v>-2</v>
@@ -1558,21 +1558,21 @@
       <c r="AB6" s="8" t="inlineStr"/>
       <c r="AC6" s="8" t="inlineStr"/>
       <c r="AD6" s="9" t="n">
-        <v>46171.91666666666</v>
+        <v>46174.42013888889</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>46171.92013888889</v>
+        <v>46174.42708333334</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>4580.38</v>
+        <v>4515.66</v>
       </c>
       <c r="AG6" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>4578.38</v>
+        <v>4517.66</v>
       </c>
       <c r="AI6" s="8" t="n">
         <v>-2</v>
@@ -1649,13 +1649,13 @@
       <c r="AB7" s="8" t="inlineStr"/>
       <c r="AC7" s="8" t="inlineStr"/>
       <c r="AD7" s="9" t="n">
-        <v>46174.42013888889</v>
+        <v>46174.61111111111</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>46174.42708333334</v>
+        <v>46174.61458333334</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>4515.66</v>
+        <v>4496.22</v>
       </c>
       <c r="AG7" s="8" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>4517.66</v>
+        <v>4498.22</v>
       </c>
       <c r="AI7" s="8" t="n">
         <v>-2</v>
@@ -1740,21 +1740,21 @@
       <c r="AB8" s="8" t="inlineStr"/>
       <c r="AC8" s="8" t="inlineStr"/>
       <c r="AD8" s="9" t="n">
-        <v>46174.61111111111</v>
+        <v>46175.45486111111</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>46174.61458333334</v>
+        <v>46175.45833333334</v>
       </c>
       <c r="AF8" s="8" t="n">
-        <v>4496.22</v>
+        <v>4501.39</v>
       </c>
       <c r="AG8" s="8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>4498.22</v>
+        <v>4499.39</v>
       </c>
       <c r="AI8" s="8" t="n">
         <v>-2</v>
@@ -1831,13 +1831,13 @@
       <c r="AB9" s="8" t="inlineStr"/>
       <c r="AC9" s="8" t="inlineStr"/>
       <c r="AD9" s="9" t="n">
-        <v>46175.45486111111</v>
+        <v>46175.50694444445</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>46175.45833333334</v>
+        <v>46175.51736111111</v>
       </c>
       <c r="AF9" s="8" t="n">
-        <v>4501.39</v>
+        <v>4520.71</v>
       </c>
       <c r="AG9" s="8" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>4499.39</v>
+        <v>4518.71</v>
       </c>
       <c r="AI9" s="8" t="n">
         <v>-2</v>
@@ -1922,21 +1922,21 @@
       <c r="AB10" s="8" t="inlineStr"/>
       <c r="AC10" s="8" t="inlineStr"/>
       <c r="AD10" s="9" t="n">
-        <v>46175.50694444445</v>
+        <v>46175.86805555555</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>46175.51736111111</v>
+        <v>46175.87152777778</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>4520.71</v>
+        <v>4502.79</v>
       </c>
       <c r="AG10" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>4518.71</v>
+        <v>4504.79</v>
       </c>
       <c r="AI10" s="8" t="n">
         <v>-2</v>
@@ -2013,13 +2013,13 @@
       <c r="AB11" s="8" t="inlineStr"/>
       <c r="AC11" s="8" t="inlineStr"/>
       <c r="AD11" s="9" t="n">
-        <v>46175.86805555555</v>
+        <v>46176.53819444445</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>46175.87152777778</v>
+        <v>46176.60416666666</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>4502.79</v>
+        <v>4455.02</v>
       </c>
       <c r="AG11" s="8" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>4504.79</v>
+        <v>4457.02</v>
       </c>
       <c r="AI11" s="8" t="n">
         <v>-2</v>
@@ -2104,13 +2104,13 @@
       <c r="AB12" s="8" t="inlineStr"/>
       <c r="AC12" s="8" t="inlineStr"/>
       <c r="AD12" s="9" t="n">
-        <v>46175.87152777778</v>
+        <v>46176.86111111111</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>46175.875</v>
+        <v>46177.08333333334</v>
       </c>
       <c r="AF12" s="8" t="n">
-        <v>4500.69</v>
+        <v>4449.2</v>
       </c>
       <c r="AG12" s="8" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="AH12" s="8" t="n">
-        <v>4502.69</v>
+        <v>4427.54</v>
       </c>
       <c r="AI12" s="8" t="n">
-        <v>-2</v>
+        <v>21.66</v>
       </c>
       <c r="AJ12" s="8" t="inlineStr"/>
       <c r="AK12" s="8" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       <c r="AM12" s="8" t="inlineStr"/>
       <c r="AN12" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>S12_BREAKOUT_UP</t>
         </is>
       </c>
       <c r="AO12" s="8" t="inlineStr"/>
@@ -2195,24 +2195,24 @@
       <c r="AB13" s="8" t="inlineStr"/>
       <c r="AC13" s="8" t="inlineStr"/>
       <c r="AD13" s="9" t="n">
-        <v>46176.53819444445</v>
+        <v>46177.86111111111</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>46176.60416666666</v>
+        <v>46177.90972222222</v>
       </c>
       <c r="AF13" s="8" t="n">
-        <v>4455.02</v>
+        <v>4458.61</v>
       </c>
       <c r="AG13" s="8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>4457.02</v>
+        <v>4514.99</v>
       </c>
       <c r="AI13" s="8" t="n">
-        <v>-2</v>
+        <v>56.38</v>
       </c>
       <c r="AJ13" s="8" t="inlineStr"/>
       <c r="AK13" s="8" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       <c r="AM13" s="8" t="inlineStr"/>
       <c r="AN13" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO13" s="8" t="inlineStr"/>
@@ -2286,13 +2286,13 @@
       <c r="AB14" s="8" t="inlineStr"/>
       <c r="AC14" s="8" t="inlineStr"/>
       <c r="AD14" s="9" t="n">
-        <v>46176.62152777778</v>
+        <v>46178.30208333334</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>46176.625</v>
+        <v>46178.35069444445</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>4451.31</v>
+        <v>4450.37</v>
       </c>
       <c r="AG14" s="8" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="AH14" s="8" t="n">
-        <v>4453.31</v>
+        <v>4452.37</v>
       </c>
       <c r="AI14" s="8" t="n">
         <v>-2</v>
@@ -2377,13 +2377,13 @@
       <c r="AB15" s="8" t="inlineStr"/>
       <c r="AC15" s="8" t="inlineStr"/>
       <c r="AD15" s="9" t="n">
-        <v>46176.86111111111</v>
+        <v>46178.82638888889</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>46177.08333333334</v>
+        <v>46178.82986111111</v>
       </c>
       <c r="AF15" s="8" t="n">
-        <v>4449.2</v>
+        <v>4414.94</v>
       </c>
       <c r="AG15" s="8" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="AH15" s="8" t="n">
-        <v>4427.54</v>
+        <v>4416.94</v>
       </c>
       <c r="AI15" s="8" t="n">
-        <v>21.66</v>
+        <v>-2</v>
       </c>
       <c r="AJ15" s="8" t="inlineStr"/>
       <c r="AK15" s="8" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       <c r="AM15" s="8" t="inlineStr"/>
       <c r="AN15" s="8" t="inlineStr">
         <is>
-          <t>S12_BREAKOUT_UP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO15" s="8" t="inlineStr"/>
@@ -2468,24 +2468,24 @@
       <c r="AB16" s="8" t="inlineStr"/>
       <c r="AC16" s="8" t="inlineStr"/>
       <c r="AD16" s="9" t="n">
-        <v>46177.86111111111</v>
+        <v>46178.86458333334</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>46177.90972222222</v>
+        <v>46178.87152777778</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>4458.61</v>
+        <v>4381.72</v>
       </c>
       <c r="AG16" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH16" s="8" t="n">
-        <v>4514.99</v>
+        <v>4383.72</v>
       </c>
       <c r="AI16" s="8" t="n">
-        <v>56.38</v>
+        <v>-2</v>
       </c>
       <c r="AJ16" s="8" t="inlineStr"/>
       <c r="AK16" s="8" t="inlineStr"/>
@@ -2493,7 +2493,7 @@
       <c r="AM16" s="8" t="inlineStr"/>
       <c r="AN16" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO16" s="8" t="inlineStr"/>
@@ -2559,13 +2559,13 @@
       <c r="AB17" s="8" t="inlineStr"/>
       <c r="AC17" s="8" t="inlineStr"/>
       <c r="AD17" s="9" t="n">
-        <v>46178.30208333334</v>
+        <v>46179.09027777778</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>46178.35069444445</v>
+        <v>46179.125</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>4450.37</v>
+        <v>4313.38</v>
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="AH17" s="8" t="n">
-        <v>4452.37</v>
+        <v>4315.38</v>
       </c>
       <c r="AI17" s="8" t="n">
         <v>-2</v>
@@ -2611,372 +2611,8 @@
       <c r="BJ17" s="8" t="inlineStr"/>
       <c r="BK17" s="8" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
-      <c r="M18" s="8" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="8" t="inlineStr"/>
-      <c r="P18" s="8" t="inlineStr"/>
-      <c r="Q18" s="8" t="inlineStr"/>
-      <c r="R18" s="8" t="inlineStr"/>
-      <c r="S18" s="8" t="inlineStr"/>
-      <c r="T18" s="8" t="inlineStr"/>
-      <c r="U18" s="8" t="inlineStr"/>
-      <c r="V18" s="8" t="inlineStr"/>
-      <c r="W18" s="8" t="inlineStr"/>
-      <c r="X18" s="8" t="inlineStr"/>
-      <c r="Y18" s="8" t="inlineStr"/>
-      <c r="Z18" s="8" t="inlineStr"/>
-      <c r="AA18" s="8" t="inlineStr"/>
-      <c r="AB18" s="8" t="inlineStr"/>
-      <c r="AC18" s="8" t="inlineStr"/>
-      <c r="AD18" s="9" t="n">
-        <v>46178.82638888889</v>
-      </c>
-      <c r="AE18" s="9" t="n">
-        <v>46178.82986111111</v>
-      </c>
-      <c r="AF18" s="8" t="n">
-        <v>4414.94</v>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH18" s="8" t="n">
-        <v>4416.94</v>
-      </c>
-      <c r="AI18" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ18" s="8" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
-      <c r="AL18" s="8" t="inlineStr"/>
-      <c r="AM18" s="8" t="inlineStr"/>
-      <c r="AN18" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO18" s="8" t="inlineStr"/>
-      <c r="AP18" s="8" t="inlineStr"/>
-      <c r="AQ18" s="8" t="inlineStr"/>
-      <c r="AR18" s="8" t="inlineStr"/>
-      <c r="AS18" s="8" t="inlineStr"/>
-      <c r="AT18" s="8" t="inlineStr"/>
-      <c r="AU18" s="8" t="inlineStr"/>
-      <c r="AV18" s="8" t="inlineStr"/>
-      <c r="AW18" s="8" t="inlineStr"/>
-      <c r="AX18" s="8" t="inlineStr"/>
-      <c r="AY18" s="8" t="inlineStr"/>
-      <c r="AZ18" s="8" t="inlineStr"/>
-      <c r="BA18" s="8" t="inlineStr"/>
-      <c r="BB18" s="8" t="inlineStr"/>
-      <c r="BC18" s="8" t="inlineStr"/>
-      <c r="BD18" s="8" t="inlineStr"/>
-      <c r="BE18" s="8" t="inlineStr"/>
-      <c r="BF18" s="8" t="inlineStr"/>
-      <c r="BG18" s="8" t="inlineStr"/>
-      <c r="BH18" s="8" t="inlineStr"/>
-      <c r="BI18" s="8" t="inlineStr"/>
-      <c r="BJ18" s="8" t="inlineStr"/>
-      <c r="BK18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="8" t="inlineStr"/>
-      <c r="Q19" s="8" t="inlineStr"/>
-      <c r="R19" s="8" t="inlineStr"/>
-      <c r="S19" s="8" t="inlineStr"/>
-      <c r="T19" s="8" t="inlineStr"/>
-      <c r="U19" s="8" t="inlineStr"/>
-      <c r="V19" s="8" t="inlineStr"/>
-      <c r="W19" s="8" t="inlineStr"/>
-      <c r="X19" s="8" t="inlineStr"/>
-      <c r="Y19" s="8" t="inlineStr"/>
-      <c r="Z19" s="8" t="inlineStr"/>
-      <c r="AA19" s="8" t="inlineStr"/>
-      <c r="AB19" s="8" t="inlineStr"/>
-      <c r="AC19" s="8" t="inlineStr"/>
-      <c r="AD19" s="9" t="n">
-        <v>46178.86458333334</v>
-      </c>
-      <c r="AE19" s="9" t="n">
-        <v>46178.87152777778</v>
-      </c>
-      <c r="AF19" s="8" t="n">
-        <v>4381.72</v>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH19" s="8" t="n">
-        <v>4383.72</v>
-      </c>
-      <c r="AI19" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ19" s="8" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
-      <c r="AL19" s="8" t="inlineStr"/>
-      <c r="AM19" s="8" t="inlineStr"/>
-      <c r="AN19" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO19" s="8" t="inlineStr"/>
-      <c r="AP19" s="8" t="inlineStr"/>
-      <c r="AQ19" s="8" t="inlineStr"/>
-      <c r="AR19" s="8" t="inlineStr"/>
-      <c r="AS19" s="8" t="inlineStr"/>
-      <c r="AT19" s="8" t="inlineStr"/>
-      <c r="AU19" s="8" t="inlineStr"/>
-      <c r="AV19" s="8" t="inlineStr"/>
-      <c r="AW19" s="8" t="inlineStr"/>
-      <c r="AX19" s="8" t="inlineStr"/>
-      <c r="AY19" s="8" t="inlineStr"/>
-      <c r="AZ19" s="8" t="inlineStr"/>
-      <c r="BA19" s="8" t="inlineStr"/>
-      <c r="BB19" s="8" t="inlineStr"/>
-      <c r="BC19" s="8" t="inlineStr"/>
-      <c r="BD19" s="8" t="inlineStr"/>
-      <c r="BE19" s="8" t="inlineStr"/>
-      <c r="BF19" s="8" t="inlineStr"/>
-      <c r="BG19" s="8" t="inlineStr"/>
-      <c r="BH19" s="8" t="inlineStr"/>
-      <c r="BI19" s="8" t="inlineStr"/>
-      <c r="BJ19" s="8" t="inlineStr"/>
-      <c r="BK19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
-      <c r="M20" s="8" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="8" t="inlineStr"/>
-      <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="8" t="inlineStr"/>
-      <c r="R20" s="8" t="inlineStr"/>
-      <c r="S20" s="8" t="inlineStr"/>
-      <c r="T20" s="8" t="inlineStr"/>
-      <c r="U20" s="8" t="inlineStr"/>
-      <c r="V20" s="8" t="inlineStr"/>
-      <c r="W20" s="8" t="inlineStr"/>
-      <c r="X20" s="8" t="inlineStr"/>
-      <c r="Y20" s="8" t="inlineStr"/>
-      <c r="Z20" s="8" t="inlineStr"/>
-      <c r="AA20" s="8" t="inlineStr"/>
-      <c r="AB20" s="8" t="inlineStr"/>
-      <c r="AC20" s="8" t="inlineStr"/>
-      <c r="AD20" s="9" t="n">
-        <v>46178.87152777778</v>
-      </c>
-      <c r="AE20" s="9" t="n">
-        <v>46178.88888888889</v>
-      </c>
-      <c r="AF20" s="8" t="n">
-        <v>4363.73</v>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH20" s="8" t="n">
-        <v>4365.73</v>
-      </c>
-      <c r="AI20" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ20" s="8" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
-      <c r="AL20" s="8" t="inlineStr"/>
-      <c r="AM20" s="8" t="inlineStr"/>
-      <c r="AN20" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO20" s="8" t="inlineStr"/>
-      <c r="AP20" s="8" t="inlineStr"/>
-      <c r="AQ20" s="8" t="inlineStr"/>
-      <c r="AR20" s="8" t="inlineStr"/>
-      <c r="AS20" s="8" t="inlineStr"/>
-      <c r="AT20" s="8" t="inlineStr"/>
-      <c r="AU20" s="8" t="inlineStr"/>
-      <c r="AV20" s="8" t="inlineStr"/>
-      <c r="AW20" s="8" t="inlineStr"/>
-      <c r="AX20" s="8" t="inlineStr"/>
-      <c r="AY20" s="8" t="inlineStr"/>
-      <c r="AZ20" s="8" t="inlineStr"/>
-      <c r="BA20" s="8" t="inlineStr"/>
-      <c r="BB20" s="8" t="inlineStr"/>
-      <c r="BC20" s="8" t="inlineStr"/>
-      <c r="BD20" s="8" t="inlineStr"/>
-      <c r="BE20" s="8" t="inlineStr"/>
-      <c r="BF20" s="8" t="inlineStr"/>
-      <c r="BG20" s="8" t="inlineStr"/>
-      <c r="BH20" s="8" t="inlineStr"/>
-      <c r="BI20" s="8" t="inlineStr"/>
-      <c r="BJ20" s="8" t="inlineStr"/>
-      <c r="BK20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr"/>
-      <c r="Q21" s="8" t="inlineStr"/>
-      <c r="R21" s="8" t="inlineStr"/>
-      <c r="S21" s="8" t="inlineStr"/>
-      <c r="T21" s="8" t="inlineStr"/>
-      <c r="U21" s="8" t="inlineStr"/>
-      <c r="V21" s="8" t="inlineStr"/>
-      <c r="W21" s="8" t="inlineStr"/>
-      <c r="X21" s="8" t="inlineStr"/>
-      <c r="Y21" s="8" t="inlineStr"/>
-      <c r="Z21" s="8" t="inlineStr"/>
-      <c r="AA21" s="8" t="inlineStr"/>
-      <c r="AB21" s="8" t="inlineStr"/>
-      <c r="AC21" s="8" t="inlineStr"/>
-      <c r="AD21" s="9" t="n">
-        <v>46179.09027777778</v>
-      </c>
-      <c r="AE21" s="9" t="n">
-        <v>46179.125</v>
-      </c>
-      <c r="AF21" s="8" t="n">
-        <v>4313.38</v>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH21" s="8" t="n">
-        <v>4315.38</v>
-      </c>
-      <c r="AI21" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ21" s="8" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
-      <c r="AL21" s="8" t="inlineStr"/>
-      <c r="AM21" s="8" t="inlineStr"/>
-      <c r="AN21" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO21" s="8" t="inlineStr"/>
-      <c r="AP21" s="8" t="inlineStr"/>
-      <c r="AQ21" s="8" t="inlineStr"/>
-      <c r="AR21" s="8" t="inlineStr"/>
-      <c r="AS21" s="8" t="inlineStr"/>
-      <c r="AT21" s="8" t="inlineStr"/>
-      <c r="AU21" s="8" t="inlineStr"/>
-      <c r="AV21" s="8" t="inlineStr"/>
-      <c r="AW21" s="8" t="inlineStr"/>
-      <c r="AX21" s="8" t="inlineStr"/>
-      <c r="AY21" s="8" t="inlineStr"/>
-      <c r="AZ21" s="8" t="inlineStr"/>
-      <c r="BA21" s="8" t="inlineStr"/>
-      <c r="BB21" s="8" t="inlineStr"/>
-      <c r="BC21" s="8" t="inlineStr"/>
-      <c r="BD21" s="8" t="inlineStr"/>
-      <c r="BE21" s="8" t="inlineStr"/>
-      <c r="BF21" s="8" t="inlineStr"/>
-      <c r="BG21" s="8" t="inlineStr"/>
-      <c r="BH21" s="8" t="inlineStr"/>
-      <c r="BI21" s="8" t="inlineStr"/>
-      <c r="BJ21" s="8" t="inlineStr"/>
-      <c r="BK21" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BK21"/>
+  <autoFilter ref="A1:BK17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3911,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK21"/>
+  <dimension ref="A1:BK17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4608,13 +4244,13 @@
       <c r="AB5" s="8" t="inlineStr"/>
       <c r="AC5" s="8" t="inlineStr"/>
       <c r="AD5" s="9" t="n">
-        <v>46171.69791666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="AE5" s="9" t="n">
-        <v>46171.70138888889</v>
+        <v>46171.92013888889</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>4539.24</v>
+        <v>4580.38</v>
       </c>
       <c r="AG5" s="8" t="inlineStr">
         <is>
@@ -4622,7 +4258,7 @@
         </is>
       </c>
       <c r="AH5" s="8" t="n">
-        <v>4537.24</v>
+        <v>4578.38</v>
       </c>
       <c r="AI5" s="8" t="n">
         <v>-2</v>
@@ -4699,21 +4335,21 @@
       <c r="AB6" s="8" t="inlineStr"/>
       <c r="AC6" s="8" t="inlineStr"/>
       <c r="AD6" s="9" t="n">
-        <v>46171.91666666666</v>
+        <v>46174.42013888889</v>
       </c>
       <c r="AE6" s="9" t="n">
-        <v>46171.92013888889</v>
+        <v>46174.42708333334</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>4580.38</v>
+        <v>4515.66</v>
       </c>
       <c r="AG6" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>4578.38</v>
+        <v>4517.66</v>
       </c>
       <c r="AI6" s="8" t="n">
         <v>-2</v>
@@ -4790,13 +4426,13 @@
       <c r="AB7" s="8" t="inlineStr"/>
       <c r="AC7" s="8" t="inlineStr"/>
       <c r="AD7" s="9" t="n">
-        <v>46174.42013888889</v>
+        <v>46174.61111111111</v>
       </c>
       <c r="AE7" s="9" t="n">
-        <v>46174.42708333334</v>
+        <v>46174.61458333334</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>4515.66</v>
+        <v>4496.22</v>
       </c>
       <c r="AG7" s="8" t="inlineStr">
         <is>
@@ -4804,7 +4440,7 @@
         </is>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>4517.66</v>
+        <v>4498.22</v>
       </c>
       <c r="AI7" s="8" t="n">
         <v>-2</v>
@@ -4881,21 +4517,21 @@
       <c r="AB8" s="8" t="inlineStr"/>
       <c r="AC8" s="8" t="inlineStr"/>
       <c r="AD8" s="9" t="n">
-        <v>46174.61111111111</v>
+        <v>46175.45486111111</v>
       </c>
       <c r="AE8" s="9" t="n">
-        <v>46174.61458333334</v>
+        <v>46175.45833333334</v>
       </c>
       <c r="AF8" s="8" t="n">
-        <v>4496.22</v>
+        <v>4501.39</v>
       </c>
       <c r="AG8" s="8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>4498.22</v>
+        <v>4499.39</v>
       </c>
       <c r="AI8" s="8" t="n">
         <v>-2</v>
@@ -4972,13 +4608,13 @@
       <c r="AB9" s="8" t="inlineStr"/>
       <c r="AC9" s="8" t="inlineStr"/>
       <c r="AD9" s="9" t="n">
-        <v>46175.45486111111</v>
+        <v>46175.50694444445</v>
       </c>
       <c r="AE9" s="9" t="n">
-        <v>46175.45833333334</v>
+        <v>46175.51736111111</v>
       </c>
       <c r="AF9" s="8" t="n">
-        <v>4501.39</v>
+        <v>4520.71</v>
       </c>
       <c r="AG9" s="8" t="inlineStr">
         <is>
@@ -4986,7 +4622,7 @@
         </is>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>4499.39</v>
+        <v>4518.71</v>
       </c>
       <c r="AI9" s="8" t="n">
         <v>-2</v>
@@ -5063,21 +4699,21 @@
       <c r="AB10" s="8" t="inlineStr"/>
       <c r="AC10" s="8" t="inlineStr"/>
       <c r="AD10" s="9" t="n">
-        <v>46175.50694444445</v>
+        <v>46175.86805555555</v>
       </c>
       <c r="AE10" s="9" t="n">
-        <v>46175.51736111111</v>
+        <v>46175.87152777778</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>4520.71</v>
+        <v>4502.79</v>
       </c>
       <c r="AG10" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>4518.71</v>
+        <v>4504.79</v>
       </c>
       <c r="AI10" s="8" t="n">
         <v>-2</v>
@@ -5154,13 +4790,13 @@
       <c r="AB11" s="8" t="inlineStr"/>
       <c r="AC11" s="8" t="inlineStr"/>
       <c r="AD11" s="9" t="n">
-        <v>46175.86805555555</v>
+        <v>46176.53819444445</v>
       </c>
       <c r="AE11" s="9" t="n">
-        <v>46175.87152777778</v>
+        <v>46176.60416666666</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>4502.79</v>
+        <v>4455.02</v>
       </c>
       <c r="AG11" s="8" t="inlineStr">
         <is>
@@ -5168,7 +4804,7 @@
         </is>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>4504.79</v>
+        <v>4457.02</v>
       </c>
       <c r="AI11" s="8" t="n">
         <v>-2</v>
@@ -5245,13 +4881,13 @@
       <c r="AB12" s="8" t="inlineStr"/>
       <c r="AC12" s="8" t="inlineStr"/>
       <c r="AD12" s="9" t="n">
-        <v>46175.87152777778</v>
+        <v>46176.86111111111</v>
       </c>
       <c r="AE12" s="9" t="n">
-        <v>46175.875</v>
+        <v>46177.08333333334</v>
       </c>
       <c r="AF12" s="8" t="n">
-        <v>4500.69</v>
+        <v>4449.2</v>
       </c>
       <c r="AG12" s="8" t="inlineStr">
         <is>
@@ -5259,10 +4895,10 @@
         </is>
       </c>
       <c r="AH12" s="8" t="n">
-        <v>4502.69</v>
+        <v>4427.54</v>
       </c>
       <c r="AI12" s="8" t="n">
-        <v>-2</v>
+        <v>21.66</v>
       </c>
       <c r="AJ12" s="8" t="inlineStr"/>
       <c r="AK12" s="8" t="inlineStr"/>
@@ -5270,7 +4906,7 @@
       <c r="AM12" s="8" t="inlineStr"/>
       <c r="AN12" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>S12_BREAKOUT_UP</t>
         </is>
       </c>
       <c r="AO12" s="8" t="inlineStr"/>
@@ -5336,24 +4972,24 @@
       <c r="AB13" s="8" t="inlineStr"/>
       <c r="AC13" s="8" t="inlineStr"/>
       <c r="AD13" s="9" t="n">
-        <v>46176.53819444445</v>
+        <v>46177.86111111111</v>
       </c>
       <c r="AE13" s="9" t="n">
-        <v>46176.60416666666</v>
+        <v>46177.90972222222</v>
       </c>
       <c r="AF13" s="8" t="n">
-        <v>4455.02</v>
+        <v>4458.61</v>
       </c>
       <c r="AG13" s="8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="AH13" s="8" t="n">
-        <v>4457.02</v>
+        <v>4514.99</v>
       </c>
       <c r="AI13" s="8" t="n">
-        <v>-2</v>
+        <v>56.38</v>
       </c>
       <c r="AJ13" s="8" t="inlineStr"/>
       <c r="AK13" s="8" t="inlineStr"/>
@@ -5361,7 +4997,7 @@
       <c r="AM13" s="8" t="inlineStr"/>
       <c r="AN13" s="8" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AO13" s="8" t="inlineStr"/>
@@ -5427,13 +5063,13 @@
       <c r="AB14" s="8" t="inlineStr"/>
       <c r="AC14" s="8" t="inlineStr"/>
       <c r="AD14" s="9" t="n">
-        <v>46176.62152777778</v>
+        <v>46178.30208333334</v>
       </c>
       <c r="AE14" s="9" t="n">
-        <v>46176.625</v>
+        <v>46178.35069444445</v>
       </c>
       <c r="AF14" s="8" t="n">
-        <v>4451.31</v>
+        <v>4450.37</v>
       </c>
       <c r="AG14" s="8" t="inlineStr">
         <is>
@@ -5441,7 +5077,7 @@
         </is>
       </c>
       <c r="AH14" s="8" t="n">
-        <v>4453.31</v>
+        <v>4452.37</v>
       </c>
       <c r="AI14" s="8" t="n">
         <v>-2</v>
@@ -5518,13 +5154,13 @@
       <c r="AB15" s="8" t="inlineStr"/>
       <c r="AC15" s="8" t="inlineStr"/>
       <c r="AD15" s="9" t="n">
-        <v>46176.86111111111</v>
+        <v>46178.82638888889</v>
       </c>
       <c r="AE15" s="9" t="n">
-        <v>46177.08333333334</v>
+        <v>46178.82986111111</v>
       </c>
       <c r="AF15" s="8" t="n">
-        <v>4449.2</v>
+        <v>4414.94</v>
       </c>
       <c r="AG15" s="8" t="inlineStr">
         <is>
@@ -5532,10 +5168,10 @@
         </is>
       </c>
       <c r="AH15" s="8" t="n">
-        <v>4427.54</v>
+        <v>4416.94</v>
       </c>
       <c r="AI15" s="8" t="n">
-        <v>21.66</v>
+        <v>-2</v>
       </c>
       <c r="AJ15" s="8" t="inlineStr"/>
       <c r="AK15" s="8" t="inlineStr"/>
@@ -5543,7 +5179,7 @@
       <c r="AM15" s="8" t="inlineStr"/>
       <c r="AN15" s="8" t="inlineStr">
         <is>
-          <t>S12_BREAKOUT_UP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO15" s="8" t="inlineStr"/>
@@ -5609,24 +5245,24 @@
       <c r="AB16" s="8" t="inlineStr"/>
       <c r="AC16" s="8" t="inlineStr"/>
       <c r="AD16" s="9" t="n">
-        <v>46177.86111111111</v>
+        <v>46178.86458333334</v>
       </c>
       <c r="AE16" s="9" t="n">
-        <v>46177.90972222222</v>
+        <v>46178.87152777778</v>
       </c>
       <c r="AF16" s="8" t="n">
-        <v>4458.61</v>
+        <v>4381.72</v>
       </c>
       <c r="AG16" s="8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="AH16" s="8" t="n">
-        <v>4514.99</v>
+        <v>4383.72</v>
       </c>
       <c r="AI16" s="8" t="n">
-        <v>56.38</v>
+        <v>-2</v>
       </c>
       <c r="AJ16" s="8" t="inlineStr"/>
       <c r="AK16" s="8" t="inlineStr"/>
@@ -5634,7 +5270,7 @@
       <c r="AM16" s="8" t="inlineStr"/>
       <c r="AN16" s="8" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="AO16" s="8" t="inlineStr"/>
@@ -5700,13 +5336,13 @@
       <c r="AB17" s="8" t="inlineStr"/>
       <c r="AC17" s="8" t="inlineStr"/>
       <c r="AD17" s="9" t="n">
-        <v>46178.30208333334</v>
+        <v>46179.09027777778</v>
       </c>
       <c r="AE17" s="9" t="n">
-        <v>46178.35069444445</v>
+        <v>46179.125</v>
       </c>
       <c r="AF17" s="8" t="n">
-        <v>4450.37</v>
+        <v>4313.38</v>
       </c>
       <c r="AG17" s="8" t="inlineStr">
         <is>
@@ -5714,7 +5350,7 @@
         </is>
       </c>
       <c r="AH17" s="8" t="n">
-        <v>4452.37</v>
+        <v>4315.38</v>
       </c>
       <c r="AI17" s="8" t="n">
         <v>-2</v>
@@ -5752,372 +5388,8 @@
       <c r="BJ17" s="8" t="inlineStr"/>
       <c r="BK17" s="8" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
-      <c r="J18" s="8" t="inlineStr"/>
-      <c r="K18" s="8" t="inlineStr"/>
-      <c r="L18" s="8" t="inlineStr"/>
-      <c r="M18" s="8" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
-      <c r="O18" s="8" t="inlineStr"/>
-      <c r="P18" s="8" t="inlineStr"/>
-      <c r="Q18" s="8" t="inlineStr"/>
-      <c r="R18" s="8" t="inlineStr"/>
-      <c r="S18" s="8" t="inlineStr"/>
-      <c r="T18" s="8" t="inlineStr"/>
-      <c r="U18" s="8" t="inlineStr"/>
-      <c r="V18" s="8" t="inlineStr"/>
-      <c r="W18" s="8" t="inlineStr"/>
-      <c r="X18" s="8" t="inlineStr"/>
-      <c r="Y18" s="8" t="inlineStr"/>
-      <c r="Z18" s="8" t="inlineStr"/>
-      <c r="AA18" s="8" t="inlineStr"/>
-      <c r="AB18" s="8" t="inlineStr"/>
-      <c r="AC18" s="8" t="inlineStr"/>
-      <c r="AD18" s="9" t="n">
-        <v>46178.82638888889</v>
-      </c>
-      <c r="AE18" s="9" t="n">
-        <v>46178.82986111111</v>
-      </c>
-      <c r="AF18" s="8" t="n">
-        <v>4414.94</v>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH18" s="8" t="n">
-        <v>4416.94</v>
-      </c>
-      <c r="AI18" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ18" s="8" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
-      <c r="AL18" s="8" t="inlineStr"/>
-      <c r="AM18" s="8" t="inlineStr"/>
-      <c r="AN18" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO18" s="8" t="inlineStr"/>
-      <c r="AP18" s="8" t="inlineStr"/>
-      <c r="AQ18" s="8" t="inlineStr"/>
-      <c r="AR18" s="8" t="inlineStr"/>
-      <c r="AS18" s="8" t="inlineStr"/>
-      <c r="AT18" s="8" t="inlineStr"/>
-      <c r="AU18" s="8" t="inlineStr"/>
-      <c r="AV18" s="8" t="inlineStr"/>
-      <c r="AW18" s="8" t="inlineStr"/>
-      <c r="AX18" s="8" t="inlineStr"/>
-      <c r="AY18" s="8" t="inlineStr"/>
-      <c r="AZ18" s="8" t="inlineStr"/>
-      <c r="BA18" s="8" t="inlineStr"/>
-      <c r="BB18" s="8" t="inlineStr"/>
-      <c r="BC18" s="8" t="inlineStr"/>
-      <c r="BD18" s="8" t="inlineStr"/>
-      <c r="BE18" s="8" t="inlineStr"/>
-      <c r="BF18" s="8" t="inlineStr"/>
-      <c r="BG18" s="8" t="inlineStr"/>
-      <c r="BH18" s="8" t="inlineStr"/>
-      <c r="BI18" s="8" t="inlineStr"/>
-      <c r="BJ18" s="8" t="inlineStr"/>
-      <c r="BK18" s="8" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr"/>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
-      <c r="M19" s="8" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
-      <c r="P19" s="8" t="inlineStr"/>
-      <c r="Q19" s="8" t="inlineStr"/>
-      <c r="R19" s="8" t="inlineStr"/>
-      <c r="S19" s="8" t="inlineStr"/>
-      <c r="T19" s="8" t="inlineStr"/>
-      <c r="U19" s="8" t="inlineStr"/>
-      <c r="V19" s="8" t="inlineStr"/>
-      <c r="W19" s="8" t="inlineStr"/>
-      <c r="X19" s="8" t="inlineStr"/>
-      <c r="Y19" s="8" t="inlineStr"/>
-      <c r="Z19" s="8" t="inlineStr"/>
-      <c r="AA19" s="8" t="inlineStr"/>
-      <c r="AB19" s="8" t="inlineStr"/>
-      <c r="AC19" s="8" t="inlineStr"/>
-      <c r="AD19" s="9" t="n">
-        <v>46178.86458333334</v>
-      </c>
-      <c r="AE19" s="9" t="n">
-        <v>46178.87152777778</v>
-      </c>
-      <c r="AF19" s="8" t="n">
-        <v>4381.72</v>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH19" s="8" t="n">
-        <v>4383.72</v>
-      </c>
-      <c r="AI19" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ19" s="8" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
-      <c r="AL19" s="8" t="inlineStr"/>
-      <c r="AM19" s="8" t="inlineStr"/>
-      <c r="AN19" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO19" s="8" t="inlineStr"/>
-      <c r="AP19" s="8" t="inlineStr"/>
-      <c r="AQ19" s="8" t="inlineStr"/>
-      <c r="AR19" s="8" t="inlineStr"/>
-      <c r="AS19" s="8" t="inlineStr"/>
-      <c r="AT19" s="8" t="inlineStr"/>
-      <c r="AU19" s="8" t="inlineStr"/>
-      <c r="AV19" s="8" t="inlineStr"/>
-      <c r="AW19" s="8" t="inlineStr"/>
-      <c r="AX19" s="8" t="inlineStr"/>
-      <c r="AY19" s="8" t="inlineStr"/>
-      <c r="AZ19" s="8" t="inlineStr"/>
-      <c r="BA19" s="8" t="inlineStr"/>
-      <c r="BB19" s="8" t="inlineStr"/>
-      <c r="BC19" s="8" t="inlineStr"/>
-      <c r="BD19" s="8" t="inlineStr"/>
-      <c r="BE19" s="8" t="inlineStr"/>
-      <c r="BF19" s="8" t="inlineStr"/>
-      <c r="BG19" s="8" t="inlineStr"/>
-      <c r="BH19" s="8" t="inlineStr"/>
-      <c r="BI19" s="8" t="inlineStr"/>
-      <c r="BJ19" s="8" t="inlineStr"/>
-      <c r="BK19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr"/>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
-      <c r="M20" s="8" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
-      <c r="O20" s="8" t="inlineStr"/>
-      <c r="P20" s="8" t="inlineStr"/>
-      <c r="Q20" s="8" t="inlineStr"/>
-      <c r="R20" s="8" t="inlineStr"/>
-      <c r="S20" s="8" t="inlineStr"/>
-      <c r="T20" s="8" t="inlineStr"/>
-      <c r="U20" s="8" t="inlineStr"/>
-      <c r="V20" s="8" t="inlineStr"/>
-      <c r="W20" s="8" t="inlineStr"/>
-      <c r="X20" s="8" t="inlineStr"/>
-      <c r="Y20" s="8" t="inlineStr"/>
-      <c r="Z20" s="8" t="inlineStr"/>
-      <c r="AA20" s="8" t="inlineStr"/>
-      <c r="AB20" s="8" t="inlineStr"/>
-      <c r="AC20" s="8" t="inlineStr"/>
-      <c r="AD20" s="9" t="n">
-        <v>46178.87152777778</v>
-      </c>
-      <c r="AE20" s="9" t="n">
-        <v>46178.88888888889</v>
-      </c>
-      <c r="AF20" s="8" t="n">
-        <v>4363.73</v>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH20" s="8" t="n">
-        <v>4365.73</v>
-      </c>
-      <c r="AI20" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ20" s="8" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
-      <c r="AL20" s="8" t="inlineStr"/>
-      <c r="AM20" s="8" t="inlineStr"/>
-      <c r="AN20" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO20" s="8" t="inlineStr"/>
-      <c r="AP20" s="8" t="inlineStr"/>
-      <c r="AQ20" s="8" t="inlineStr"/>
-      <c r="AR20" s="8" t="inlineStr"/>
-      <c r="AS20" s="8" t="inlineStr"/>
-      <c r="AT20" s="8" t="inlineStr"/>
-      <c r="AU20" s="8" t="inlineStr"/>
-      <c r="AV20" s="8" t="inlineStr"/>
-      <c r="AW20" s="8" t="inlineStr"/>
-      <c r="AX20" s="8" t="inlineStr"/>
-      <c r="AY20" s="8" t="inlineStr"/>
-      <c r="AZ20" s="8" t="inlineStr"/>
-      <c r="BA20" s="8" t="inlineStr"/>
-      <c r="BB20" s="8" t="inlineStr"/>
-      <c r="BC20" s="8" t="inlineStr"/>
-      <c r="BD20" s="8" t="inlineStr"/>
-      <c r="BE20" s="8" t="inlineStr"/>
-      <c r="BF20" s="8" t="inlineStr"/>
-      <c r="BG20" s="8" t="inlineStr"/>
-      <c r="BH20" s="8" t="inlineStr"/>
-      <c r="BI20" s="8" t="inlineStr"/>
-      <c r="BJ20" s="8" t="inlineStr"/>
-      <c r="BK20" s="8" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>BACKTEST_ONLY</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>NO_SAME_SIDE_CANDIDATE</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr"/>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
-      <c r="M21" s="8" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
-      <c r="O21" s="8" t="inlineStr"/>
-      <c r="P21" s="8" t="inlineStr"/>
-      <c r="Q21" s="8" t="inlineStr"/>
-      <c r="R21" s="8" t="inlineStr"/>
-      <c r="S21" s="8" t="inlineStr"/>
-      <c r="T21" s="8" t="inlineStr"/>
-      <c r="U21" s="8" t="inlineStr"/>
-      <c r="V21" s="8" t="inlineStr"/>
-      <c r="W21" s="8" t="inlineStr"/>
-      <c r="X21" s="8" t="inlineStr"/>
-      <c r="Y21" s="8" t="inlineStr"/>
-      <c r="Z21" s="8" t="inlineStr"/>
-      <c r="AA21" s="8" t="inlineStr"/>
-      <c r="AB21" s="8" t="inlineStr"/>
-      <c r="AC21" s="8" t="inlineStr"/>
-      <c r="AD21" s="9" t="n">
-        <v>46179.09027777778</v>
-      </c>
-      <c r="AE21" s="9" t="n">
-        <v>46179.125</v>
-      </c>
-      <c r="AF21" s="8" t="n">
-        <v>4313.38</v>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="AH21" s="8" t="n">
-        <v>4315.38</v>
-      </c>
-      <c r="AI21" s="8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ21" s="8" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
-      <c r="AL21" s="8" t="inlineStr"/>
-      <c r="AM21" s="8" t="inlineStr"/>
-      <c r="AN21" s="8" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="AO21" s="8" t="inlineStr"/>
-      <c r="AP21" s="8" t="inlineStr"/>
-      <c r="AQ21" s="8" t="inlineStr"/>
-      <c r="AR21" s="8" t="inlineStr"/>
-      <c r="AS21" s="8" t="inlineStr"/>
-      <c r="AT21" s="8" t="inlineStr"/>
-      <c r="AU21" s="8" t="inlineStr"/>
-      <c r="AV21" s="8" t="inlineStr"/>
-      <c r="AW21" s="8" t="inlineStr"/>
-      <c r="AX21" s="8" t="inlineStr"/>
-      <c r="AY21" s="8" t="inlineStr"/>
-      <c r="AZ21" s="8" t="inlineStr"/>
-      <c r="BA21" s="8" t="inlineStr"/>
-      <c r="BB21" s="8" t="inlineStr"/>
-      <c r="BC21" s="8" t="inlineStr"/>
-      <c r="BD21" s="8" t="inlineStr"/>
-      <c r="BE21" s="8" t="inlineStr"/>
-      <c r="BF21" s="8" t="inlineStr"/>
-      <c r="BG21" s="8" t="inlineStr"/>
-      <c r="BH21" s="8" t="inlineStr"/>
-      <c r="BI21" s="8" t="inlineStr"/>
-      <c r="BJ21" s="8" t="inlineStr"/>
-      <c r="BK21" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BK21"/>
+  <autoFilter ref="A1:BK17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6656,10 +5928,10 @@
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>46170.4375</v>
@@ -6685,10 +5957,10 @@
         </is>
       </c>
       <c r="D3" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>46170.96875</v>
@@ -6772,10 +6044,10 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>42.04</v>
+        <v>50.04</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>46170.4375</v>
@@ -6801,10 +6073,10 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-2.34</v>
+        <v>3.66</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>46170.4375</v>
@@ -6830,10 +6102,10 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>44.38</v>
+        <v>46.38</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>46170.96875</v>

--- a/excel_reports/backtest_compare/s12/compare_s12_M5_20260528_0800_20260608_1000.xlsx
+++ b/excel_reports/backtest_compare/s12/compare_s12_M5_20260528_0800_20260608_1000.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Live Only'!$A$1:$BK$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backtest Only'!$A$1:$BK$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Matches'!$A$1:$BK$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Gap Summary'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-18 17:19:59</t>
+          <t>2026-06-19 17:08:39</t>
         </is>
       </c>
     </row>
@@ -5862,10 +5862,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -6056,66 +6056,8 @@
         <v>46179.09027777778</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>46170.4375</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>46179.09027777778</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>bt_s14_family</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>46170.96875</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>46177.86111111111</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>